--- a/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA_UNION</t>
+          <t>LA UNION</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>14059</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.3988</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-80.74290000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>523</v>
-      </c>
-      <c r="J2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.3988</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-80.7429</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>14061</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.376383</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-80.732394</v>
-      </c>
-      <c r="I3" t="n">
-        <v>516</v>
-      </c>
-      <c r="J3" t="n">
-        <v>34</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.376383</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-80.732394</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>14064</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.394623</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-80.760846</v>
-      </c>
-      <c r="I4" t="n">
-        <v>261</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.394623</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-80.760846</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>14065</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.37564</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-80.778599</v>
-      </c>
-      <c r="I5" t="n">
-        <v>317</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.37564</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-80.778599</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>14070 JESUS ES MI MAESTRO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.4062</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-80.7426</v>
-      </c>
-      <c r="I6" t="n">
-        <v>437</v>
-      </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.4062</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-80.7426</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>HERMANOS MELENDEZ</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.4017</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-80.7406</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1723</v>
-      </c>
-      <c r="J7" t="n">
-        <v>75</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.4017</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-80.7406</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.384324</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-80.764777</v>
-      </c>
-      <c r="I8" t="n">
-        <v>941</v>
-      </c>
-      <c r="J8" t="n">
-        <v>51</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.384324</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-80.764777</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>SAN SEBASTIAN</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.4029</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-80.74200999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>175</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.4029</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-80.74201</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>SAN JOSE</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.40461</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-80.74534</v>
-      </c>
-      <c r="I10" t="n">
-        <v>107</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.40461</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-80.74534</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>1056</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.4074</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-80.74550000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>38</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.4074</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-80.7455</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.402155</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-80.742563</v>
-      </c>
-      <c r="I12" t="n">
-        <v>704</v>
-      </c>
-      <c r="J12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.402155</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-80.742563</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>TNTE E P CESAR PINGLO CHUNGA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.4053</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-80.74357999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>292</v>
-      </c>
-      <c r="J13" t="n">
-        <v>34</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.4053</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-80.74358</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>14062 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.383608</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-80.76489100000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>896</v>
-      </c>
-      <c r="J14" t="n">
-        <v>34</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.383608</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-80.764891</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,22 +1315,94 @@
           <t>LIBERTADORES DE AMERICA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.38953</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-80.74012</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1295</v>
-      </c>
-      <c r="J15" t="n">
-        <v>50</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.38953</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-80.74012</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>200110</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LA UNION</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>414793</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>15367</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.378781</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.726607</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>414665</t>
+          <t>414632</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>755</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.3988</t>
+          <t>-5.4053</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.7429</t>
+          <t>-80.7484</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>414670</t>
+          <t>414509</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.376383</t>
+          <t>-5.40446</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.732394</t>
+          <t>-80.74616</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>414825</t>
+          <t>647504</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HERMANOS MELENDEZ</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.4017</t>
+          <t>-5.40461</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.7406</t>
+          <t>-80.74534</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>414854</t>
+          <t>722857</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.384324</t>
+          <t>-5.402155</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.764777</t>
+          <t>-80.742563</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>704</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>414892</t>
+          <t>660406</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.4029</t>
+          <t>-5.4074</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.74201</t>
+          <t>-80.7455</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>647504</t>
+          <t>414665</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.40461</t>
+          <t>-5.3988</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.74534</t>
+          <t>-80.7429</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>523</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>660406</t>
+          <t>414670</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.4074</t>
+          <t>-5.376383</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.7455</t>
+          <t>-80.732394</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>516</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>722857</t>
+          <t>770221</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>TNTE E P CESAR PINGLO CHUNGA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.402155</t>
+          <t>-5.4053</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.742563</t>
+          <t>-80.74358</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>292</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,27 +1183,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>770221</t>
+          <t>770240</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TNTE E P CESAR PINGLO CHUNGA</t>
+          <t>14062 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.4053</t>
+          <t>-5.383608</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.74358</t>
+          <t>-80.764891</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>896</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>770240</t>
+          <t>857568</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14062 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>LIBERTADORES DE AMERICA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.383608</t>
+          <t>-5.38953</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.764891</t>
+          <t>-80.74012</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>857568</t>
+          <t>414854</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LIBERTADORES DE AMERICA</t>
+          <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.38953</t>
+          <t>-5.384324</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.74012</t>
+          <t>-80.764777</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>941</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,40 +1369,164 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>414825</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>HERMANOS MELENDEZ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.4017</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.7406</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>200110</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LA UNION</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>414892</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SAN SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.4029</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-80.74201</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>200110</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LA UNION</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>414793</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>15367</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>-5.378781</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>-80.726607</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>144</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.402155</t>
+          <t>-5.39092310966967</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.742563</t>
+          <t>-80.7409529423287</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>414632</t>
+          <t>857568</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>LIBERTADORES DE AMERICA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.4053</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.7484</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-5.38953</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-80.74012</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>414509</t>
+          <t>770240</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>14062 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.40446</t>
+          <t>896</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.74616</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>-5.383608</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-80.764891</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>414694</t>
+          <t>770221</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>TNTE E P CESAR PINGLO CHUNGA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.394623</t>
+          <t>292</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.760846</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-5.4053</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-80.74358</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>414707</t>
+          <t>722857</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.37564</t>
+          <t>704</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.778599</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>-5.39092310966967</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-80.7409529423287</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>414750</t>
+          <t>660406</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14070 JESUS ES MI MAESTRO</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.4062</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.7426</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>-5.4074</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-80.7455</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>-5.40461</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-80.74534</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>722857</t>
+          <t>414892</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.39092310966967</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.7409529423287</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>-5.4029</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-80.74201</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>660406</t>
+          <t>414854</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.4074</t>
+          <t>941</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.7455</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-5.384324</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-80.764777</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>414665</t>
+          <t>414825</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>HERMANOS MELENDEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.3988</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.7429</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>-5.4017</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-80.7406</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>414670</t>
+          <t>414793</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.376383</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.732394</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>-5.378781</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.726607</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>770221</t>
+          <t>414750</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TNTE E P CESAR PINGLO CHUNGA</t>
+          <t>14070 JESUS ES MI MAESTRO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.4053</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.74358</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>-5.4062</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.7426</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>770240</t>
+          <t>414707</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14062 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.383608</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.764891</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>-5.37564</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.778599</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>857568</t>
+          <t>414694</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LIBERTADORES DE AMERICA</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.38953</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.74012</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>-5.394623</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-80.760846</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>414854</t>
+          <t>414670</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.384324</t>
+          <t>516</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.764777</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>-5.376383</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-80.732394</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>414825</t>
+          <t>414665</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HERMANOS MELENDEZ</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.4017</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.7406</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>-5.3988</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-80.7429</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>414892</t>
+          <t>414632</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN</t>
+          <t>755</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.4029</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.74201</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>-5.4053</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-80.7484</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>414793</t>
+          <t>414509</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>059</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.378781</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.726607</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>-5.40446</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-80.74616</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-LA_UNION.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
